--- a/data/trans_camb/P8_2_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P8_2_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,06</t>
+          <t>-1,47; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,82</t>
+          <t>-1,8; 5,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,56</t>
+          <t>-0,73; 7,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,99</t>
+          <t>-0,84; 8,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,45</t>
+          <t>-2,3; 6,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 1,82</t>
+          <t>-7,34; 1,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 6,07</t>
+          <t>-0,14; 6,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,08</t>
+          <t>-1,17; 5,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,8</t>
+          <t>-2,6; 3,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 49,32</t>
+          <t>-9,17; 53,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 47,39</t>
+          <t>-11,52; 45,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 59,55</t>
+          <t>-4,92; 57,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 37,69</t>
+          <t>-3,34; 37,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 31,01</t>
+          <t>-8,85; 32,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 8,28</t>
+          <t>-29,01; 8,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 35,72</t>
+          <t>-0,87; 35,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 29,9</t>
+          <t>-6,04; 29,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 22,16</t>
+          <t>-13,04; 19,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,72</t>
+          <t>0,19; 6,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,35</t>
+          <t>-1,8; 4,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 50,38</t>
+          <t>-1,77; 51,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,73</t>
+          <t>-1,28; 6,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 5,15</t>
+          <t>-2,31; 5,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,24</t>
+          <t>-3,52; 3,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,61</t>
+          <t>0,65; 5,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,05</t>
+          <t>-0,84; 4,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 32,7</t>
+          <t>-1,21; 32,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 58,79</t>
+          <t>1,36; 59,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 37,52</t>
+          <t>-12,71; 35,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 429,5</t>
+          <t>-13,1; 430,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 32,13</t>
+          <t>-5,42; 30,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 24,79</t>
+          <t>-9,41; 28,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 15,86</t>
+          <t>-13,81; 16,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 34,34</t>
+          <t>3,18; 33,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 24,22</t>
+          <t>-4,38; 24,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 191,5</t>
+          <t>-6,75; 185,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 0,91</t>
+          <t>-6,74; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 2,11</t>
+          <t>-5,23; 2,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,52</t>
+          <t>-1,8; 6,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 2,49</t>
+          <t>-6,05; 2,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,89</t>
+          <t>-7,83; 1,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -2,14</t>
+          <t>-18,45; -1,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,64</t>
+          <t>-5,26; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,48</t>
+          <t>-5,37; 0,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 0,5</t>
+          <t>-8,8; 0,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 6,08</t>
+          <t>-37,92; 8,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 16,19</t>
+          <t>-30,46; 17,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 47,67</t>
+          <t>-9,94; 49,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 10,95</t>
+          <t>-22,3; 12,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 4,11</t>
+          <t>-29,01; 4,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,88; -9,19</t>
+          <t>-67,7; -7,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 3,43</t>
+          <t>-23,57; 4,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 2,59</t>
+          <t>-24,78; 3,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 2,0</t>
+          <t>-41,53; 2,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 6,05</t>
+          <t>-0,69; 5,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,6</t>
+          <t>-3,11; 3,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,08</t>
+          <t>-1,77; 4,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,38</t>
+          <t>0,96; 8,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 1,54</t>
+          <t>-5,77; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,57</t>
+          <t>-4,96; 4,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,24</t>
+          <t>1,24; 6,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,76</t>
+          <t>-3,24; 1,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,24</t>
+          <t>-2,26; 3,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 47,88</t>
+          <t>-4,49; 45,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 29,54</t>
+          <t>-20,26; 26,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 32,97</t>
+          <t>-11,83; 33,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 39,61</t>
+          <t>3,86; 41,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 7,56</t>
+          <t>-23,41; 9,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 16,76</t>
+          <t>-20,42; 19,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 35,76</t>
+          <t>6,32; 38,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 10,12</t>
+          <t>-16,57; 10,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 18,46</t>
+          <t>-11,47; 17,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,48</t>
+          <t>-0,18; 3,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,32</t>
+          <t>-1,03; 2,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 24,28</t>
+          <t>0,84; 25,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,56</t>
+          <t>0,34; 4,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,64</t>
+          <t>-2,45; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; -0,03</t>
+          <t>-6,76; -0,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,68; 3,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,38</t>
+          <t>-1,31; 1,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 13,18</t>
+          <t>-1,1; 11,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 26,39</t>
+          <t>-1,09; 25,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 17,95</t>
+          <t>-6,91; 18,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,08; 178,12</t>
+          <t>5,74; 192,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,4; 20,51</t>
+          <t>1,45; 20,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 7,44</t>
+          <t>-9,98; 6,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -0,79</t>
+          <t>-28,14; -0,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,42; 19,11</t>
+          <t>3,23; 18,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 7,71</t>
+          <t>-6,77; 7,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 72,82</t>
+          <t>-5,77; 63,55</t>
         </is>
       </c>
     </row>
